--- a/results/cluster_ga/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
@@ -647,16 +647,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.40927533267089</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.53210548740752</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.10056481337324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.67448993661435</v>
+        <v>22.8670703876311</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.11820774969988</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.3115383399637</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.75053880099027</v>
       </c>
     </row>
   </sheetData>
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.44956249583923</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.42225166188175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.48009433254258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.62354712310802</v>
+        <v>19.92180266748164</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.25467453629894</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.98537800725755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.31283457909049</v>
       </c>
     </row>
   </sheetData>
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.42105707141883</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.90194673259661</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.44529471729091</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.39501751552813</v>
+        <v>31.4777580708385</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.3603636208333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.53371504321766</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.25981383869088</v>
       </c>
     </row>
   </sheetData>
@@ -821,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.91728614692117</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.13190283583295</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.77059215322376</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.71742352017485</v>
+        <v>27.0003440448125</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.40950964123234</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.18386996497623</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.48030954909081</v>
       </c>
     </row>
   </sheetData>
@@ -879,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.80552258575858</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.68034987948526</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.98253993648498</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.43199767240756</v>
+        <v>25.76765558069653</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.37387564149402</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.09640612803203</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.1534149173612</v>
       </c>
     </row>
   </sheetData>
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.80715649666637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.39741413192219</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.40949257505783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.1187921437092</v>
+        <v>26.27975848591773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.34214617989809</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.31372799615163</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.07972040240575</v>
       </c>
     </row>
   </sheetData>
@@ -995,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.77344343322785</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.40905844129549</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.12757569359172</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.12369889507771</v>
+        <v>26.69666240637761</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.26575089970459</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.72987135126034</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.82214629381101</v>
       </c>
     </row>
   </sheetData>
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.07504007571361</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.98047881334032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.6244658662233</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.90908304294025</v>
+        <v>29.58532056820162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.42312455773229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.55828072546009</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.63247415996508</v>
       </c>
     </row>
   </sheetData>
@@ -1111,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.91107652208466</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.70490703431173</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.44769318474287</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.41110983800952</v>
+        <v>25.93129312309218</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.54945511666444</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.37773102230689</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.35100278214543</v>
       </c>
     </row>
   </sheetData>
@@ -1169,16 +1169,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.68399361488046</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.06707836488765</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.52682292476499</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.24418095076842</v>
+        <v>23.29119251356855</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.87436055745659</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.09779577056272</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.64643857841514</v>
       </c>
     </row>
   </sheetData>
@@ -1227,16 +1227,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.34707104651241</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.41380582018272</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.48963007725356</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.634941098877</v>
+        <v>31.37504146158341</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.05589634521267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.21778237592429</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.13566844328002</v>
       </c>
     </row>
   </sheetData>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.11149467363203</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.21051211866993</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.89682384590124</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.96129102007086</v>
+        <v>27.4193234701565</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.66403590305133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.13309044172476</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.38584173989582</v>
       </c>
     </row>
   </sheetData>
@@ -1343,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.05987916087097</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.91358699806335</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.03277369831725</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.1753814205134</v>
+        <v>33.19519624173504</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.21551679907322</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.54297472671817</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.69093835280644</v>
       </c>
     </row>
   </sheetData>
@@ -1401,16 +1401,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.39510098176251</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.49152839769057</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.10190511239205</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.73779675181045</v>
+        <v>27.00097342946999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.20047510708257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.23565994911691</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.67306232450361</v>
       </c>
     </row>
   </sheetData>
@@ -1459,16 +1459,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.57634408122374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.87797230309366</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.46336830468663</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.62063667162997</v>
+        <v>27.28061459023426</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.77625852956992</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.1484386020593</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.77893481116756</v>
       </c>
     </row>
   </sheetData>
@@ -1517,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.8393251543679</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.95300592245243</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.14794077760745</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.39462089574268</v>
+        <v>27.76796338641605</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.09443066002621</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.25110444427901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.56045421264457</v>
       </c>
     </row>
   </sheetData>
@@ -1575,16 +1575,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.22733043017169</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.29696112331191</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.74382432696772</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.40814300053333</v>
+        <v>26.40067537241903</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.84860342714547</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.53226404332274</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.80028329721894</v>
       </c>
     </row>
   </sheetData>
@@ -1633,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.9285189679471</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.84640091641565</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.77176098007678</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.34727816001348</v>
+        <v>30.62283261928525</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.78319676965926</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.61249140886198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.56241607469411</v>
       </c>
     </row>
   </sheetData>
@@ -1691,16 +1691,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.10317966609319</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.12910141328915</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.14456855939094</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.36075279187048</v>
+        <v>27.82198769430896</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.08823948157289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.7123615395504</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.48093231700195</v>
       </c>
     </row>
   </sheetData>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.49633844190103</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.11262052775261</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.8302408616962</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.9132326340004</v>
+        <v>26.16814870779307</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.66714563908518</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.47626257367669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.76733662777923</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.50914218315864</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.63599559917965</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.25194268713542</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.58013316017984</v>
+        <v>27.59464658746195</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.28811067523349</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.97013102388913</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.77847320265413</v>
       </c>
     </row>
   </sheetData>
@@ -1865,16 +1865,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.73671628737979</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.41741051224241</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.59505405549815</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.35721155622268</v>
+        <v>22.73680470494457</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.32466780795546</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.05619651212999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.91763292367154</v>
       </c>
     </row>
   </sheetData>
@@ -1923,16 +1923,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.01652855338316</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.52774950138739</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.56468753937268</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.23560837992984</v>
+        <v>35.50190642418997</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.65189529389913</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.93338557160538</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.12104092507449</v>
       </c>
     </row>
   </sheetData>
@@ -1981,16 +1981,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.27935868194668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.73164947030001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.36927743872495</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.63326973905449</v>
+        <v>31.38452136665508</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.16756338084283</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.64371138864887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.81646382832096</v>
       </c>
     </row>
   </sheetData>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.96508945045799</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.28099594674505</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.41820269349511</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.63013949254634</v>
+        <v>18.87369879911777</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.72971078888531</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.88950462033147</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.23140255781377</v>
       </c>
     </row>
   </sheetData>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.26916086381162</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.20508940534229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.53247204526512</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.47458370993574</v>
+        <v>33.82626331019467</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.60824326507032</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.15921918831362</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.18601304878916</v>
       </c>
     </row>
   </sheetData>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.53168255649064</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.82784187930717</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.33070506380561</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.74149556607351</v>
+        <v>22.35604321188033</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.8011641922158</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.09417770655747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.72965767738675</v>
       </c>
     </row>
   </sheetData>
@@ -2213,16 +2213,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.8482512997603</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.53851227653325</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.16867209403199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.53453443396625</v>
+        <v>23.92032374372705</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.76763539031933</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.78030496029801</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.67066487329661</v>
       </c>
     </row>
   </sheetData>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.00066364507905</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.23932725199628</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.36647674815606</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.31597633690079</v>
+        <v>28.30074056951929</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.1708509774321</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.69100113441475</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.12259299298618</v>
       </c>
     </row>
   </sheetData>
@@ -2329,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.82158110650992</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.18427638948813</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.80797183657106</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.3074339299915</v>
+        <v>30.59531335794618</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.33215493480383</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.87550218695587</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.35437901736131</v>
       </c>
     </row>
   </sheetData>
@@ -2387,16 +2387,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.70910194886962</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.66534891054325</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.01440361941364</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.5075657415569</v>
+        <v>23.15829336751105</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.06629784861184</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.8079323199788</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.98108808899511</v>
       </c>
     </row>
   </sheetData>
@@ -2445,16 +2445,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.70281247979421</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.42627957351694</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.88018725129081</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.86909361447811</v>
+        <v>22.33978254906538</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.20869424456587</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.18416344095621</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.91001821790474</v>
       </c>
     </row>
   </sheetData>
@@ -2503,16 +2503,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.86653219956003</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.57475286797881</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.80711738207453</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.70967666615454</v>
+        <v>26.90825126462058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.78012380814464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.80669123164342</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.09607688905129</v>
       </c>
     </row>
   </sheetData>
@@ -2561,16 +2561,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.7211173889137</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.20530400160152</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.96810226537517</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.78393514716776</v>
+        <v>24.49407159999591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.93246322157316</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.02399992410426</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.9255800981863</v>
       </c>
     </row>
   </sheetData>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.44025628507526</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.8252677606389</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.89639490904616</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.08215956214638</v>
+        <v>22.53555012864088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.79144787657434</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.28920584201717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.03027306333528</v>
       </c>
     </row>
   </sheetData>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.72027880028082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.48059795738247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.79632009314187</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.42032073970033</v>
+        <v>28.84741238621578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.18636365742057</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.64148598671562</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.04334705300398</v>
       </c>
     </row>
   </sheetData>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.25670336518374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.21585039348021</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.16812617932852</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.94923150479498</v>
+        <v>27.84256226422023</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.72776386810344</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.3056040076119</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.2001058791747</v>
       </c>
     </row>
   </sheetData>
@@ -2793,16 +2793,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.45320201310077</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.79517291330274</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.10228037091092</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.97615539119212</v>
+        <v>24.2863212054018</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.82847289096794</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.61821137230564</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.32181254853217</v>
       </c>
     </row>
   </sheetData>
@@ -2851,16 +2851,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.76435125840209</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.45576068958916</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.05575723880112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.13120214114143</v>
+        <v>22.36458546890037</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.76588579750448</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.8197442112637</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.14629660323681</v>
       </c>
     </row>
   </sheetData>
@@ -2909,16 +2909,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.55528439403694</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.98095249786097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.76644820466255</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.44003180858714</v>
+        <v>23.5703916159895</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.95169606640699</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.18322083790626</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.23845370249582</v>
       </c>
     </row>
   </sheetData>
@@ -2967,16 +2967,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.1250805200463</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.84585496476737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.93000827210819</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.80831718230312</v>
+        <v>27.24747909895904</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.39603320184073</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.37426137897289</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.91694301904239</v>
       </c>
     </row>
   </sheetData>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.37395654754956</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.57177827539316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.46820507195217</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.59410390133912</v>
+        <v>22.69556094596653</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.34240530438819</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.02596810994823</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.93755575162304</v>
       </c>
     </row>
   </sheetData>
@@ -3083,16 +3083,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.06507269324477</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.88445798660289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.01878647037311</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.67439860564237</v>
+        <v>25.99992596407997</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.10420766211342</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.38363764763452</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.52515862970431</v>
       </c>
     </row>
   </sheetData>
@@ -3141,16 +3141,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.39176661097522</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.87985324309512</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.33242154535982</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.74115946907978</v>
+        <v>23.26151411426735</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.51662858901163</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.40940531054954</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.38360594294795</v>
       </c>
     </row>
   </sheetData>
@@ -3199,16 +3199,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.628886640926</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.53469956826789</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.36571931883547</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.95363450583239</v>
+        <v>24.09591843234363</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.55760726516568</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.51899701893329</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.64511302493514</v>
       </c>
     </row>
   </sheetData>
@@ -3257,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.99021762856594</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.10930513596423</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.57778710683816</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.49027156812171</v>
+        <v>22.06810632968464</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.2717844308816</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.2035626270047</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.87085213035607</v>
       </c>
     </row>
   </sheetData>
@@ -3315,16 +3315,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.69426014640505</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.66605571081691</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.87709283547612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.25191544934768</v>
+        <v>24.60946862646578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.10967362945566</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.95782191460679</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.82876634690049</v>
       </c>
     </row>
   </sheetData>
@@ -3373,16 +3373,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.76145078473107</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.56489362104089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.2146427703964</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.99702040261022</v>
+        <v>24.46160586868655</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.49680780299888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.01041592725436</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.8502714367363</v>
       </c>
     </row>
   </sheetData>
@@ -3431,16 +3431,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.54179012592967</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.51100823492728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.7587426423783</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.58443810098236</v>
+        <v>27.61801396576575</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.73345044745491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.82067128928736</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.87509649635625</v>
       </c>
     </row>
   </sheetData>
@@ -3489,16 +3489,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.40203823090241</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.58842642439295</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.18309525911156</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.39817041713215</v>
+        <v>27.44817730758838</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.63653826673728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.92291645628075</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.16905626424137</v>
       </c>
     </row>
   </sheetData>
@@ -3547,16 +3547,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.27559733667356</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.16388422203716</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.94052484898562</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.37605230881772</v>
+        <v>24.43086819085649</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.63646878861879</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.5285100407864</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.07114775359893</v>
       </c>
     </row>
   </sheetData>
@@ -3605,16 +3605,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.19278166732914</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.5271631913499</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.55323279359603</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.01615544206382</v>
+        <v>25.52122868526428</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.95104589402883</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.37476129288775</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.07587127103297</v>
       </c>
     </row>
   </sheetData>
@@ -3663,16 +3663,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.77916918508578</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.25956491233431</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.74185983967208</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.85781689005815</v>
+        <v>25.68975827939162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.11085058239102</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.13967934045112</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.00922723848788</v>
       </c>
     </row>
   </sheetData>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.09688546711274</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.88306187798952</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.28481015131782</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.267033613622</v>
+        <v>23.14692006726149</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.4899662447266</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.07618259523705</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.66051445516158</v>
       </c>
     </row>
   </sheetData>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.35801898073416</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.66930432578491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.06402204491229</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.67658373987607</v>
+        <v>30.74771909607412</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.99075468614865</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.87840959854562</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.98793528379774</v>
       </c>
     </row>
   </sheetData>
@@ -3837,16 +3837,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.68253055379112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.69195717038034</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.76909351340336</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.08760953918501</v>
+        <v>25.02891623851714</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.03990494108292</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.52278656629334</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.39743246577617</v>
       </c>
     </row>
   </sheetData>
@@ -3895,16 +3895,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.81673711993928</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.12656897484175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.84966258348167</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.34512125824956</v>
+        <v>21.86991106310228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.73555544181115</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.36118118155173</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.11409539464713</v>
       </c>
     </row>
   </sheetData>
@@ -3953,16 +3953,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.08339832163867</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.32370319460882</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.4394534143463</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.87067702429666</v>
+        <v>22.04861238592937</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.64129750781805</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.44767801765201</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.6981559044611</v>
       </c>
     </row>
   </sheetData>
@@ -4011,16 +4011,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.96228694664653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.58752817839576</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.39478805226726</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.9503660274952</v>
+        <v>36.24486144550085</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.15575750985569</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.28880360851619</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.2848263655853</v>
       </c>
     </row>
   </sheetData>
@@ -4069,16 +4069,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.08136901013963</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.31789342860287</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.29448029340023</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.25745755794264</v>
+        <v>29.10338560105978</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.52707233423407</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.03475371557596</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.97503945527393</v>
       </c>
     </row>
   </sheetData>
@@ -4127,16 +4127,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.82367551628979</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.59827484242155</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.05841929635623</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.55797725563697</v>
+        <v>24.19529615887982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.26207778788606</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.16642942513103</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.91778436464798</v>
       </c>
     </row>
   </sheetData>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.18952620312406</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.25969228007665</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.90030337075623</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.9477069410877</v>
+        <v>29.04703733548873</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.72268366592759</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.70144376865317</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.14129293688643</v>
       </c>
     </row>
   </sheetData>
@@ -4243,16 +4243,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.86704851600829</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.09972783764871</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.56477489221908</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.45407617592807</v>
+        <v>32.47309803057132</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.85981147053562</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.42748016381603</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.38160368430512</v>
       </c>
     </row>
   </sheetData>
@@ -4301,16 +4301,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.49948319009685</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.53141598099644</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.98658324611252</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.39699692371369</v>
+        <v>21.6324988022118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.25721966791688</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.7498021136649</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.21088015900215</v>
       </c>
     </row>
   </sheetData>
@@ -4359,16 +4359,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.49034083768814</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.83305330049828</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.54181459051212</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.23560764928558</v>
+        <v>27.44968502046329</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.44330072272064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.12773848787083</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.32482537619425</v>
       </c>
     </row>
   </sheetData>
@@ -4417,16 +4417,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.05141295068031</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.84112770690344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.92566530600253</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.96709723456994</v>
+        <v>26.53682866981685</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.86106020485902</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.2413455981578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.3156678579921</v>
       </c>
     </row>
   </sheetData>
@@ -4475,16 +4475,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.60835594256012</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.82279655441364</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.05474987372069</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.40513274791819</v>
+        <v>21.27246603819618</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.13520256985089</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.3433286077958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.99668597895659</v>
       </c>
     </row>
   </sheetData>
@@ -4533,16 +4533,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.68283521727327</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.03564890156704</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.47695963456874</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.98081666286921</v>
+        <v>27.94036904222231</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.42851902382382</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.91796602223149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.32316946917042</v>
       </c>
     </row>
   </sheetData>
@@ -4591,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.18255278864904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.01011833223454</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.39571985545475</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.10754319921395</v>
+        <v>23.59110904468088</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.53602510600434</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.77151539838355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.06380993089122</v>
       </c>
     </row>
   </sheetData>
@@ -4649,16 +4649,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.80696673466046</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.66560018234076</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.24460258357011</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.17219037495703</v>
+        <v>22.24139726926921</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.74506035968516</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.68940478214785</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.75545046320417</v>
       </c>
     </row>
   </sheetData>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.50613235280285</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.45752519609527</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.39091572144773</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.30029653994991</v>
+        <v>25.08757347158749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.72237978171734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.38382164352265</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.99707732372693</v>
       </c>
     </row>
   </sheetData>
@@ -4765,16 +4765,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.75130658689706</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.71203581897671</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.61528816537058</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.36443772692752</v>
+        <v>28.00200051031216</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.99228361152541</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.03789761331648</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.17613749622142</v>
       </c>
     </row>
   </sheetData>
@@ -4823,16 +4823,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.11258245667811</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.32782116787826</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.24226424929722</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.20500551548042</v>
+        <v>27.11430568106416</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.57772162773308</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.96088709315455</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.61861893367444</v>
       </c>
     </row>
   </sheetData>
@@ -4881,16 +4881,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.65614843092464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.48553378849205</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.54707194442848</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.67271668003202</v>
+        <v>29.6398055402667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.13411746668267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.56776752529507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.90039474551276</v>
       </c>
     </row>
   </sheetData>
@@ -4939,16 +4939,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36035555300321</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.51843178839915</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.52055127805719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>18.77551532315765</v>
+        <v>23.55392356098784</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.63403059742981</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.81476414112283</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.19192213583818</v>
       </c>
     </row>
   </sheetData>
@@ -4997,16 +4997,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.81682255693958</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.46043943142404</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.75044598488022</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.76769423288867</v>
+        <v>26.03728516361543</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.11196364583758</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.24230519485842</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.68005114552422</v>
       </c>
     </row>
   </sheetData>
@@ -5055,16 +5055,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.9999334291606</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.30533103628485</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.24386518744674</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.53432012456595</v>
+        <v>23.21832613973464</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.40661440437141</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.66351286203176</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.09769818248882</v>
       </c>
     </row>
   </sheetData>
@@ -5113,16 +5113,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.10956880164148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.5836024192725</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.10736847365898</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.97015977360442</v>
+        <v>26.55107730482803</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.94888601868024</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.73651284233445</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.19147030498477</v>
       </c>
     </row>
   </sheetData>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.83596032649452</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.48212117953124</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.39909864417258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.42857843360972</v>
+        <v>24.99151783847232</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.59024752914296</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.60830788884639</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.17716243408959</v>
       </c>
     </row>
   </sheetData>
@@ -5229,16 +5229,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.15440659707001</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.86618653955694</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.9721149205359</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.41990612151247</v>
+        <v>27.52615687500729</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.76154791950644</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.22155979818498</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.66596716192451</v>
       </c>
     </row>
   </sheetData>
@@ -5287,16 +5287,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.01193843599473</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.58502525892163</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.90685412367914</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.71829930622243</v>
+        <v>26.56887590607214</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.59772902066193</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.28465906340661</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.53464168773822</v>
       </c>
     </row>
   </sheetData>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.63400647043821</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.30457738479992</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.47862389497974</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.09182005990445</v>
+        <v>31.83013072877401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.44407735486547</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.29991940103669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.83575412950947</v>
       </c>
     </row>
   </sheetData>
@@ -5403,16 +5403,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.30696008924205</v>
-      </c>
-      <c r="C2" t="n">
-        <v>44.69209319727997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.70569770279295</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.2526572499597</v>
+        <v>30.79479384028899</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.64308476560269</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.34109493243299</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.38427038467779</v>
       </c>
     </row>
   </sheetData>
@@ -5461,16 +5461,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6374509581677</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.91516406456528</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.17406367688649</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.66713038379064</v>
+        <v>20.25710027230192</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.46147394424103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.47449092365964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.13504955019271</v>
       </c>
     </row>
   </sheetData>
@@ -5519,16 +5519,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.61757876818868</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.97830079808327</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.47156631007539</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.60503769657432</v>
+        <v>22.07277152832475</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.20246624568138</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.66036646340146</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.17600717043953</v>
       </c>
     </row>
   </sheetData>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.51283497803344</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.97696416185823</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.25965682436865</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.55405350021969</v>
+        <v>31.23593735227402</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.59667095287234</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.36083895436368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.89542681509042</v>
       </c>
     </row>
   </sheetData>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.58608756359879</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.35398504628906</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.16360588698517</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.99001352619846</v>
+        <v>34.1001399586163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.18021712315737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.36403036635842</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.800004828866</v>
       </c>
     </row>
   </sheetData>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.99844494676718</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.23896056195609</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.76254976942692</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.25898396973371</v>
+        <v>24.00948286867809</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.72433980967077</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.2323543811999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.05898852818435</v>
       </c>
     </row>
   </sheetData>
@@ -5751,16 +5751,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.25090702310028</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.93323259046512</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.08792002840496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.97420316995966</v>
+        <v>33.51015403247593</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.9528792915785</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.4302526512726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.69449805722328</v>
       </c>
     </row>
   </sheetData>
@@ -5809,16 +5809,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.04193105214837</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.09172345802872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.75448785816149</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.91529955004271</v>
+        <v>28.21839988710272</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.24326290412223</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.57880293393754</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.22792026194234</v>
       </c>
     </row>
   </sheetData>
@@ -5867,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.02014645095112</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.01357621659793</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.11893704392269</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.31999980331636</v>
+        <v>26.45619892491549</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.89169420091021</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.72537621301495</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.95792304297392</v>
       </c>
     </row>
   </sheetData>
@@ -5925,16 +5925,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.41455166405355</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.66915479187115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.28081928467242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.39771751802335</v>
+        <v>24.5367883360896</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.06054271195938</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.56556798680212</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.77632738822557</v>
       </c>
     </row>
   </sheetData>
@@ -5983,16 +5983,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.23028192284648</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.09236611443295</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.37086773059336</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.1755094548493</v>
+        <v>19.87431183330341</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.94692400661581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.07241105103279</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.48714902996197</v>
       </c>
     </row>
   </sheetData>
@@ -6041,16 +6041,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.69746595048289</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.63086104297449</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.17631226115635</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.34512005707032</v>
+        <v>23.28804437206716</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.5161781952843</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.02944847089632</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.04972377352954</v>
       </c>
     </row>
   </sheetData>
@@ -6099,16 +6099,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.86132155170544</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.48595262156222</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.23764103111107</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.60600707901597</v>
+        <v>28.09208201090574</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.56641858468279</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.87100624876769</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.11744000254573</v>
       </c>
     </row>
   </sheetData>
@@ -6157,16 +6157,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.97997989233656</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.98895916572884</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.10280081706647</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.03354341017579</v>
+        <v>29.6042367180534</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.55941168815474</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.5606384172928</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.22087899990748</v>
       </c>
     </row>
   </sheetData>
@@ -6215,16 +6215,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.71585850336539</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.54115683868147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.84862488179686</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41.45087978662846</v>
+        <v>27.70037050731483</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.4527311125187</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.26824886989669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.36955785955943</v>
       </c>
     </row>
   </sheetData>
@@ -6273,16 +6273,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.85108807267262</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.65440580876577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.75705902100781</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.26049176829118</v>
+        <v>31.56230000286084</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.80608404919499</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.7645897051958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.82275239365206</v>
       </c>
     </row>
   </sheetData>
@@ -6331,16 +6331,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.47429071695217</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.85141716907187</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.41624521011703</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.48183450467112</v>
+        <v>25.53572057726154</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.02992965608254</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.82032148612855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.91612757665646</v>
       </c>
     </row>
   </sheetData>
@@ -6389,16 +6389,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.24589883479497</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.83456824883074</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.33624844876613</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.52275040396867</v>
+        <v>21.16653939722251</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.32428933720114</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.95302234625871</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.93047292694977</v>
       </c>
     </row>
   </sheetData>
@@ -6447,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.3695706680706</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.51010622938689</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.07915754483632</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.42700585911343</v>
+        <v>27.61723920407733</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.17616179467485</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.15649184010281</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.48749443299902</v>
       </c>
     </row>
   </sheetData>
@@ -6505,16 +6505,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.9966260466213</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.42577991549023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.63555001608355</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.13180788305588</v>
+        <v>32.27507638833644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.73635719241777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.4811718559404</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.08534992206389</v>
       </c>
     </row>
   </sheetData>
@@ -6563,16 +6563,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.44987672334008</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.59903527017612</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.43192469426669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.048783457336</v>
+        <v>24.31170178645302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.00284011107468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.67058796237478</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.14703198350104</v>
       </c>
     </row>
   </sheetData>
@@ -6621,16 +6621,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.276086899955</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.87006120201286</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.91647354413875</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.92708796552799</v>
+        <v>26.73112912581223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.76643767425199</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.65943432086317</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.25857513308554</v>
       </c>
     </row>
   </sheetData>
@@ -6679,16 +6679,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.86803821191771</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.91725743672639</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.38520576849309</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.65708223545349</v>
+        <v>22.64104765316482</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.12923507185468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.83012380532293</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.02836763702145</v>
       </c>
     </row>
   </sheetData>
@@ -6737,16 +6737,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.45291796154279</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.31547157326406</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.78569719394974</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.01315443246429</v>
+        <v>24.61226795181475</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.60288199813402</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.85278773938407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.3474994382156</v>
       </c>
     </row>
   </sheetData>
@@ -6795,16 +6795,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.3410611054017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.20121122557398</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.02376711792822</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.06146675497166</v>
+        <v>33.75881364159382</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.28922135434799</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.33769750180796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.52400875357747</v>
       </c>
     </row>
   </sheetData>
@@ -6853,16 +6853,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.19979021422483</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.83861415304968</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.83008852355275</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.1566115394324</v>
+        <v>23.46067877986412</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.52433203396068</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.73966024819799</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.48661597926545</v>
       </c>
     </row>
   </sheetData>
@@ -6911,16 +6911,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.19924786856961</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.1244174061514</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.31176442338407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.67065513032351</v>
+        <v>27.77559759079321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.63896980122468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.49106890355869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.69521260193334</v>
       </c>
     </row>
   </sheetData>
@@ -6969,16 +6969,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.87362238675148</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.04917948533457</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.23931234734083</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.07344293662208</v>
+        <v>20.08324609740851</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.94066076268728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.24622219754747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.57343437778933</v>
       </c>
     </row>
   </sheetData>
@@ -7027,16 +7027,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.16079089187267</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.80543698490829</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.94911777141497</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.3131895944137</v>
+        <v>28.42887836127492</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.67427730880395</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.53759532105384</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.31080827701128</v>
       </c>
     </row>
   </sheetData>
@@ -7085,16 +7085,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.65637967726164</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.3629308896348</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.69411086920977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.09055008667942</v>
+        <v>21.22453504617758</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.98567760877527</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.24004215276875</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.83443434210572</v>
       </c>
     </row>
   </sheetData>
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.70011368876477</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.06045268448038</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.37600892580037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.52391998299125</v>
+        <v>22.20131223091251</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.17382195286744</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.55558405117642</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.86377872449048</v>
       </c>
     </row>
   </sheetData>
@@ -7201,16 +7201,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.09572344143042</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.7846428593335</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.53233829871156</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.7306257700288</v>
+        <v>24.42378324140617</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.36914664976506</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.49703311944107</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.88946328067515</v>
       </c>
     </row>
   </sheetData>
@@ -7259,16 +7259,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17.23077278080392</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41.87685369859651</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.44279236029258</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.01854363250257</v>
+        <v>30.62070249617978</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.12747647086523</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.85696009145059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.98038075040492</v>
       </c>
     </row>
   </sheetData>
@@ -7317,16 +7317,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.2833989945627</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.80577248588969</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.73586541756095</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.97381627566296</v>
+        <v>32.73206314228344</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.28854364255366</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.45204334075875</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.60273857791254</v>
       </c>
     </row>
   </sheetData>
@@ -7375,16 +7375,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.08754178049786</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.70540507269502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.79802486222222</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.44623137352094</v>
+        <v>25.34092535352846</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.8140607144605</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.26027554712361</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.10457290776556</v>
       </c>
     </row>
   </sheetData>
@@ -7433,16 +7433,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.05738214091875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.93139586073923</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.63406363298983</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.89713831439666</v>
+        <v>31.40526232838031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.47934309397779</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.38404589750905</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.4150457512902</v>
       </c>
     </row>
   </sheetData>
@@ -7491,16 +7491,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.27138496521919</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.73023063243946</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.2990664047418</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.31570417779486</v>
+        <v>21.58141713756175</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.16783882558407</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.56690082005774</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.74232508714947</v>
       </c>
     </row>
   </sheetData>
@@ -7549,16 +7549,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.69988684707316</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.32205323259662</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.05479344430858</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.63396017295345</v>
+        <v>28.73271127721324</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.42821193211716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.51742940588569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.5938168558411</v>
       </c>
     </row>
   </sheetData>
@@ -7607,16 +7607,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.92901902414702</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.52212678893356</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.39464037947007</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.69184340073808</v>
+        <v>22.65140088994234</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.16858925052891</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.49124860953419</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.32368560325879</v>
       </c>
     </row>
   </sheetData>
@@ -7665,16 +7665,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.69095502286357</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.70154622977419</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.81192914533499</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.68363140009831</v>
+        <v>26.25251389061006</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.77829120775837</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.60290437838869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.98857814446581</v>
       </c>
     </row>
   </sheetData>
@@ -7723,16 +7723,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.01734665226114</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.13493676067468</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.68479126984719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.12650475190756</v>
+        <v>24.26308296427621</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.40063364513722</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.03953019780866</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.56082755304413</v>
       </c>
     </row>
   </sheetData>
@@ -7781,16 +7781,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.34247315774958</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.17031038776655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.68581055991353</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.57867742009044</v>
+        <v>22.08156139356045</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.85489317519463</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.28792771194696</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.42438934488316</v>
       </c>
     </row>
   </sheetData>
@@ -7839,16 +7839,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.44681202851888</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.23998470096003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.26330968840762</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.92771752002886</v>
+        <v>20.78878206894154</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.11753894118117</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.06894597525298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.61636722753994</v>
       </c>
     </row>
   </sheetData>
@@ -7897,16 +7897,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.7832343121009</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.88151570701667</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.34462684423695</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.20451387027366</v>
+        <v>30.29840408409904</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39.25552763274315</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.11857948463658</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.46089863498251</v>
       </c>
     </row>
   </sheetData>
@@ -7955,16 +7955,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.11653781266618</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.94224648839817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.36417608596135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.27107130692523</v>
+        <v>31.36753778414554</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.8350090695754</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.48413223926529</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.59100021520323</v>
       </c>
     </row>
   </sheetData>
@@ -8013,16 +8013,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.45758793180306</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.35758418190456</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.37905129837592</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.35027645436847</v>
+        <v>34.36551327292732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.66754442564242</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.90587993975663</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.71861398335534</v>
       </c>
     </row>
   </sheetData>
@@ -8071,16 +8071,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.27974607919938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.44571187002421</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.54118488593065</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.39371525755304</v>
+        <v>23.72454383217152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.9205307932515</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.49322021183077</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.3998533595271</v>
       </c>
     </row>
   </sheetData>
@@ -8129,16 +8129,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.15556555054563</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.87559572843079</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.63192176156025</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.526663245257</v>
+        <v>33.42918555469345</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.41902797367771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.31265750896958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.11550235096016</v>
       </c>
     </row>
   </sheetData>
@@ -8187,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.79217908999363</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.93337966964818</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.55168152973857</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.10480980537504</v>
+        <v>29.36653586975332</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.02869113328206</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.62630687405999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.09537173915441</v>
       </c>
     </row>
   </sheetData>
@@ -8245,16 +8245,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.39153894974131</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.29632886621748</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.58892325735114</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.04621635277778</v>
+        <v>28.50510996408562</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.69145008294715</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.93146627979407</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.65171729149739</v>
       </c>
     </row>
   </sheetData>
@@ -8303,16 +8303,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.88244041768817</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.68706483913631</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.99514572129833</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.56364907546739</v>
+        <v>24.79088904857825</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.61222246312339</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.07204736874858</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.86840273509561</v>
       </c>
     </row>
   </sheetData>
@@ -8361,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.49305722082096</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.85988061747623</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.79073122580406</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.9952250610826</v>
+        <v>28.48528764375502</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.91078074265446</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.52118600238613</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.64985507246607</v>
       </c>
     </row>
   </sheetData>
@@ -8419,16 +8419,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.60080273280489</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.57451555813322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.00756696187271</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.56049551453033</v>
+        <v>30.64674715003235</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.62434928981678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.682859048181</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.28504422880145</v>
       </c>
     </row>
   </sheetData>
@@ -8477,16 +8477,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.08836372806019</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.26460310058207</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.99052613997799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.29395540690088</v>
+        <v>23.67045092998618</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.74965202702556</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.27587096199368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.27930707154471</v>
       </c>
     </row>
   </sheetData>
@@ -8535,16 +8535,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.95378982435157</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.42816177347692</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.1111239928594</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.74202263848266</v>
+        <v>21.74443581155417</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.5995480895363</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.39145963162835</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.61731963616262</v>
       </c>
     </row>
   </sheetData>
@@ -8593,16 +8593,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.64876482270589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.2659931028697</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.82022968101768</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.12044656810656</v>
+        <v>26.11491356145943</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.70634943053948</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.11724884615669</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.446607310166</v>
       </c>
     </row>
   </sheetData>
@@ -8651,16 +8651,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36971621856621</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.28318638362926</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.28750107522562</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.20815115082312</v>
+        <v>26.08270156572236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.20071277231349</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.50225799005791</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.18613951060583</v>
       </c>
     </row>
   </sheetData>
@@ -8709,16 +8709,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.06283133272488</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.25301456482757</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.21974638744846</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.51968205570152</v>
+        <v>26.35547926245935</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.92839456046226</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.80071017087214</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.30775598343965</v>
       </c>
     </row>
   </sheetData>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.65493406566387</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.4636858651818</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.62981921149548</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.17306178028737</v>
+        <v>22.43561014697074</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.75454952659655</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.30520505463432</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.87718845345925</v>
       </c>
     </row>
   </sheetData>
@@ -8825,16 +8825,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.44285603911705</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.4312658261119</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.45191147182248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.3303412150442</v>
+        <v>24.45753057896062</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.02972508196771</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.45097066773948</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.10317158402287</v>
       </c>
     </row>
   </sheetData>
@@ -8883,16 +8883,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.18864390501781</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.15626814053916</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.61909397757033</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.1000556975374</v>
+        <v>24.4447514784652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.68606379422872</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.09539880197706</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.19402267751637</v>
       </c>
     </row>
   </sheetData>
@@ -8941,16 +8941,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.40237788281938</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.68651825168666</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.98801639884119</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.57528711686775</v>
+        <v>23.23128281323094</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.74027531780411</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.7174807936711</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.83005634366582</v>
       </c>
     </row>
   </sheetData>
@@ -8999,16 +8999,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.12755380520009</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.81782999310651</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.44052001533083</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.92122631459967</v>
+        <v>35.53711666956806</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.46992495086997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.98876453244543</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.11449923411589</v>
       </c>
     </row>
   </sheetData>
@@ -9057,16 +9057,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.92203535186316</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.45567429628903</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.50432918910422</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.42126818197452</v>
+        <v>24.51378102497732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.62026480818406</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.22445337456463</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.69080497189766</v>
       </c>
     </row>
   </sheetData>
@@ -9115,16 +9115,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.92703447465028</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.95745042597686</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.55603780282684</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.79625330917762</v>
+        <v>22.55800986545785</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.74018105285802</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.49230841363843</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.84601347002296</v>
       </c>
     </row>
   </sheetData>
@@ -9173,16 +9173,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.12450641724288</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.12639821831719</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.28645120869703</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.86855093228267</v>
+        <v>26.51583495505674</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.9882646736765</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.53356490209448</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.68226491458693</v>
       </c>
     </row>
   </sheetData>
@@ -9231,16 +9231,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.19771654737815</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.16437412107791</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.45683766777847</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.0830071576763</v>
+        <v>20.41778396148619</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.09024930606929</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.58361099633112</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.13978207590538</v>
       </c>
     </row>
   </sheetData>
@@ -9289,16 +9289,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.51158188366329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.66454516895374</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.61137051534496</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.63390882682534</v>
+        <v>25.55212959424263</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.51346777298009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.53907874367088</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.05133888416304</v>
       </c>
     </row>
   </sheetData>
@@ -9347,16 +9347,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.89313393825982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.84071961593635</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.45685678049358</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.52407601658891</v>
+        <v>26.29024998148098</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.34880044905264</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.22054528136674</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.92886193022277</v>
       </c>
     </row>
   </sheetData>
@@ -9405,16 +9405,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.27736090690912</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.33624231789501</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.65834410758428</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.49344678176166</v>
+        <v>24.64771510964102</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.60028426928867</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.61056259250315</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.87767581554468</v>
       </c>
     </row>
   </sheetData>
@@ -9463,16 +9463,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.32575680870113</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.11085756073735</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.33197007469734</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.71504896219471</v>
+        <v>27.48338857994118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.66775866276802</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.34572695575272</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.38903759038313</v>
       </c>
     </row>
   </sheetData>
@@ -9521,16 +9521,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.99324078465377</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.89013560399662</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.05886570395791</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.64086071773729</v>
+        <v>25.43049903436569</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.92877364139211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.68693152720535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.7068525724662</v>
       </c>
     </row>
   </sheetData>
@@ -9579,16 +9579,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.42115572670134</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.88494817841824</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.56919851870042</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.10388674432709</v>
+        <v>26.71963387398924</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.54428123013414</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.01799397578532</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.9760716806741</v>
       </c>
     </row>
   </sheetData>
@@ -9637,16 +9637,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.22439094773571</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.72114750015558</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.81570917490764</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.8206181584465</v>
+        <v>26.53054425762647</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.9872467251596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.45272401271436</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.49048935645866</v>
       </c>
     </row>
   </sheetData>
@@ -9695,16 +9695,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.25072608833827</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40.21022209451919</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.87252059526031</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.30298356602869</v>
+        <v>24.95112128518456</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.22540212545389</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.30322708572568</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.72153363855868</v>
       </c>
     </row>
   </sheetData>
@@ -9753,16 +9753,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.88414269583401</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.15115106300204</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.35668643202305</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.70751172284043</v>
+        <v>31.55346017071397</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.70411047517615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.80232106615885</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.07132109790517</v>
       </c>
     </row>
   </sheetData>
@@ -9811,16 +9811,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.92841761974493</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.2845178130888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.23397270687691</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.83525788134238</v>
+        <v>28.12325312682031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.99729121739196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.49432638856047</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.92926511806226</v>
       </c>
     </row>
   </sheetData>
@@ -9869,16 +9869,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.73969342371296</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.0348485337547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.73853620135633</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.45708417762698</v>
+        <v>37.22684681614589</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.92745040385268</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.64999026136199</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.96852457431837</v>
       </c>
     </row>
   </sheetData>
@@ -9927,16 +9927,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.68402431927191</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.30614497945129</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.17886144382004</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.46977864514209</v>
+        <v>26.43939459972689</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.68614929347193</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.0121666181811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.15152318450034</v>
       </c>
     </row>
   </sheetData>
@@ -9985,16 +9985,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.51235013453183</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.143379992226</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.58414803387691</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.27018263429196</v>
+        <v>32.78496285812741</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.6065936120151</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.34874848208294</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.12483075186657</v>
       </c>
     </row>
   </sheetData>
@@ -10043,16 +10043,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.95251912624902</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.91424515043909</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.48920683913466</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.04988054645746</v>
+        <v>29.6847076140374</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.25122411921726</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.5725425380659</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.7488252569001</v>
       </c>
     </row>
   </sheetData>
@@ -10101,16 +10101,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.40642574024264</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.80420641315788</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.93226169733938</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.21728087842321</v>
+        <v>25.69894190581788</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.52934553257462</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.49063330829811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.40889348583611</v>
       </c>
     </row>
   </sheetData>
@@ -10159,16 +10159,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.30393813436363</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.42688665142886</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.07622183740087</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.06124644183678</v>
+        <v>28.81437465063341</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.97610704201825</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.97324429385035</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.15073695082612</v>
       </c>
     </row>
   </sheetData>
@@ -10217,16 +10217,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.22317350716401</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.72973073281261</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.81873682222008</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.59398343199489</v>
+        <v>24.75961116829694</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.57903868476672</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.86325509154755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.17816144104314</v>
       </c>
     </row>
   </sheetData>
@@ -10275,16 +10275,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.43298167660016</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.84883244761586</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.07259909720166</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.90172447750109</v>
+        <v>25.58887609518634</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.11017707524821</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.52562283262777</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.03397735872694</v>
       </c>
     </row>
   </sheetData>
@@ -10333,16 +10333,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.11272952164891</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.43146253496002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.01898439677969</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.40183086376943</v>
+        <v>24.70499804235228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.73150265532229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.32370036527516</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.7028055738104</v>
       </c>
     </row>
   </sheetData>
@@ -10391,16 +10391,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.22384073370221</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.65667568304006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.6335934665232</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.31709171749464</v>
+        <v>36.48984836589432</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.71453601370998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.85395150139458</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.00227415840569</v>
       </c>
     </row>
   </sheetData>
@@ -10449,16 +10449,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.48625441376656</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.55306720011976</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.09360424623943</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.47697481218984</v>
+        <v>24.14616436685747</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.33976553239929</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.33420695741589</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.74311700122147</v>
       </c>
     </row>
   </sheetData>
@@ -10507,16 +10507,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.99023171024664</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.92531902306466</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.19798422200115</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.09961660286311</v>
+        <v>25.2067437635604</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.54243023537781</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.87145809384086</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.43886159324275</v>
       </c>
     </row>
   </sheetData>
@@ -10565,16 +10565,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.24372520116161</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.00889465290093</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.44235440857786</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.00659006222812</v>
+        <v>28.16115206303732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.75517563237857</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.36696593741391</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.69799433609796</v>
       </c>
     </row>
   </sheetData>
@@ -10623,16 +10623,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.83705910870304</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.93835507295764</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.10410172744068</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.99504644054176</v>
+        <v>22.43757962940773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.06967003116378</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.78543731519757</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.86695963685291</v>
       </c>
     </row>
   </sheetData>
@@ -10681,16 +10681,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.22113532614005</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.80056528981774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.35906909897719</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.38899951151258</v>
+        <v>22.53529413302474</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.80598171790349</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.87957663378016</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.710944182083</v>
       </c>
     </row>
   </sheetData>
@@ -10739,16 +10739,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.82395178695069</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.51854003967584</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.84927936665246</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.65135612092615</v>
+        <v>29.22588039174817</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.14740676670073</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.60465628483396</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.2970683062965</v>
       </c>
     </row>
   </sheetData>
@@ -10797,16 +10797,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.89014017331308</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.96755656516675</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.65008190808092</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.95006896744229</v>
+        <v>30.02334737463848</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.73444184881296</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.56548275546553</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.3349158861665</v>
       </c>
     </row>
   </sheetData>
@@ -10855,16 +10855,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.882819477099</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.45896511998638</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.25271513319054</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.99505843519088</v>
+        <v>24.01474155646964</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.67612464245869</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.0594445726864</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.27284787973424</v>
       </c>
     </row>
   </sheetData>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.84438851463511</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.85450611989556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.20295435571869</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.28199667127987</v>
+        <v>36.40234149026404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.53761799117198</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.82221978047283</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.92208041890649</v>
       </c>
     </row>
   </sheetData>
@@ -10971,16 +10971,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.43487988243896</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.74624579126018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>37.33246148186834</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.58210283274608</v>
+        <v>31.24065048473133</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.76445708617059</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.20274445641254</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.48176169194657</v>
       </c>
     </row>
   </sheetData>
@@ -11029,16 +11029,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.56335601166146</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.69517206439838</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.80031531942139</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.41806822051076</v>
+        <v>19.45455621453894</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.45358190932311</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.1099764570839</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.69622722862463</v>
       </c>
     </row>
   </sheetData>
@@ -11087,16 +11087,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.41489665626372</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.54070596659454</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48.19836914790123</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.92374471759062</v>
+        <v>27.1669417680338</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.77976678480196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.03289216544004</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.54158758621421</v>
       </c>
     </row>
   </sheetData>
@@ -11145,16 +11145,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.98890760644587</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.96131796902387</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.54731760810583</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.58006084690343</v>
+        <v>24.56568924672953</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.39260014085091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.72521440985132</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.16364801115536</v>
       </c>
     </row>
   </sheetData>
@@ -11203,16 +11203,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.23668390881282</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.31402306847239</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.15603616338221</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.5597792616421</v>
+        <v>22.818029309787</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.23195081976495</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.95954651812355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.1104656477183</v>
       </c>
     </row>
   </sheetData>
@@ -11261,16 +11261,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.17564198095697</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.4526824611046</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.65314682367425</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.11179075665226</v>
+        <v>24.92326940201664</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.1390104457284</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.3631366968842</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.72069999962174</v>
       </c>
     </row>
   </sheetData>
@@ -11319,16 +11319,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.04089213768534</v>
-      </c>
-      <c r="C2" t="n">
-        <v>43.42096516936393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.14916198628705</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.49644637636462</v>
+        <v>27.31554321148539</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.12415862317662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.38248396365938</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.41980394414498</v>
       </c>
     </row>
   </sheetData>
@@ -11377,16 +11377,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28418536470265</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.52224284448678</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.14675563546133</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.75154654058539</v>
+        <v>28.73362505016982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.50922723300449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.354124341315</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.25525682914443</v>
       </c>
     </row>
   </sheetData>
@@ -11435,16 +11435,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.08676728728269</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.20309093854436</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.66507456940234</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.53844314771575</v>
+        <v>25.23739880111637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.20577676435479</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.89268519330775</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.8452274502844</v>
       </c>
     </row>
   </sheetData>
@@ -11493,16 +11493,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.18962624028761</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.86246041645046</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.29637036927925</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.92086567879099</v>
+        <v>27.62996845929269</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.15254128701596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.85669859523163</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.22672842065663</v>
       </c>
     </row>
   </sheetData>
@@ -11551,16 +11551,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.3031141563204</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.58544650607774</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.12367855361387</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.47400512092433</v>
+        <v>29.10362327552092</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.00657571956171</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.18036297115513</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.4522946319598</v>
       </c>
     </row>
   </sheetData>
@@ -11609,16 +11609,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.26205937115154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.20471149007001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.93976397400836</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.3601528785285</v>
+        <v>24.2148783048662</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.98551227481525</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.22916809670898</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.27235367059615</v>
       </c>
     </row>
   </sheetData>
@@ -11667,16 +11667,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.45232679491071</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.10621970994536</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.51192579188991</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.84113432354217</v>
+        <v>26.19193622918903</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.99631031334548</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.70752563357608</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.89368272600924</v>
       </c>
     </row>
   </sheetData>
@@ -11725,16 +11725,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.94573171990848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.23087342435766</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.1946696160674</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.07058670245217</v>
+        <v>21.00260785590583</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.20588847955089</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.2723775260034</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.33409598687366</v>
       </c>
     </row>
   </sheetData>
@@ -11783,16 +11783,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.94576794315532</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.58287807371637</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.6783229502776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>38.80893510358229</v>
+        <v>27.22727156247125</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.34686761731635</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.79435473655084</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.81207774791658</v>
       </c>
     </row>
   </sheetData>
@@ -11841,16 +11841,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.10639248029315</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.75386378629367</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.62586681398196</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.10548646734868</v>
+        <v>32.07907587331125</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.93984354996116</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.46876466585767</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.82726799265308</v>
       </c>
     </row>
   </sheetData>
@@ -11899,16 +11899,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.77113333678315</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.17194646400864</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.23267496601085</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.37452824948094</v>
+        <v>23.90858572233839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.63774903596466</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.37215242758549</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.81350800657257</v>
       </c>
     </row>
   </sheetData>
@@ -11957,16 +11957,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.48425555242448</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.45903271029226</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.78176785758455</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.5020689160407</v>
+        <v>26.23652437535225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.59693180192017</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.80212477109368</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.52459273051716</v>
       </c>
     </row>
   </sheetData>
@@ -12015,16 +12015,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.42812315666393</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.93793395056112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.28056896290184</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.24760567574682</v>
+        <v>27.19795015408201</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.63356575373142</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.37452734192947</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.47653877710542</v>
       </c>
     </row>
   </sheetData>
@@ -12073,16 +12073,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.24181109062749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>38.55467894903827</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.52351710421622</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.53992887784443</v>
+        <v>28.73767836115437</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.14170570809938</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.8793010769412</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.41181087193388</v>
       </c>
     </row>
   </sheetData>
@@ -12131,16 +12131,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.00469553658171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.20419075178513</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.77345417492687</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.55536101458905</v>
+        <v>28.47996364111591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.79815424796553</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.75844043298636</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.45634338999608</v>
       </c>
     </row>
   </sheetData>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.01824854484708</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35.3838149629229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.05976803519404</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.58357140988078</v>
+        <v>20.14544430646333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.42748587895924</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.32745623209004</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.57016577346349</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
@@ -647,16 +647,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.8670703876311</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.11820774969988</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.3115383399637</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.75053880099027</v>
+        <v>29.99756864569348</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.41646472988683</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.17184448327556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.86633174519887</v>
       </c>
     </row>
   </sheetData>
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.92180266748164</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.25467453629894</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.98537800725755</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.31283457909049</v>
+        <v>32.6164894439263</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.70448726400009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.39660544007581</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.8768907960431</v>
       </c>
     </row>
   </sheetData>
@@ -763,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.4777580708385</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.3603636208333</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.53371504321766</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.25981383869088</v>
+        <v>27.07752003364219</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.47046244446284</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.42792086235886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.36873699395178</v>
       </c>
     </row>
   </sheetData>
@@ -821,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.0003440448125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.40950964123234</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.18386996497623</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.48030954909081</v>
+        <v>22.67864539210073</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.73521105797685</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.40309482997474</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.85681982953064</v>
       </c>
     </row>
   </sheetData>
@@ -879,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.76765558069653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.37387564149402</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.09640612803203</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.1534149173612</v>
+        <v>26.56897106511401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.66539703279615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.98747487611444</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.85625235023168</v>
       </c>
     </row>
   </sheetData>
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.27975848591773</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.34214617989809</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.31372799615163</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.07972040240575</v>
+        <v>30.84952568534431</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.89208288016281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.07017432623152</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.2281977414365</v>
       </c>
     </row>
   </sheetData>
@@ -995,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.69666240637761</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.26575089970459</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.72987135126034</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.82214629381101</v>
+        <v>27.60922048993718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.76961807409831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.12495534461901</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.36094856480461</v>
       </c>
     </row>
   </sheetData>
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.58532056820162</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.42312455773229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.55828072546009</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.63247415996508</v>
+        <v>24.76846668044617</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.95510085799142</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.29786297861765</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.67875060332088</v>
       </c>
     </row>
   </sheetData>
@@ -1111,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.93129312309218</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.54945511666444</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.37773102230689</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.35100278214543</v>
+        <v>29.4480122729096</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.1239693808842</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.77320127371304</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.99613899041194</v>
       </c>
     </row>
   </sheetData>
@@ -1169,16 +1169,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.29119251356855</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.87436055745659</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.09779577056272</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.64643857841514</v>
+        <v>27.47301047190491</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.06074699226677</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.56812379857497</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.43349754111654</v>
       </c>
     </row>
   </sheetData>
@@ -1227,16 +1227,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.37504146158341</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.05589634521267</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.21778237592429</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.13566844328002</v>
+        <v>26.64771598581743</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.64172834347201</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.43920842881471</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.87904506212369</v>
       </c>
     </row>
   </sheetData>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.4193234701565</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.66403590305133</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.13309044172476</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.38584173989582</v>
+        <v>28.77552592093252</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.30030411674615</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.97144595719766</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.68534872585369</v>
       </c>
     </row>
   </sheetData>
@@ -1343,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.19519624173504</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.21551679907322</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.54297472671817</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.69093835280644</v>
+        <v>25.84356641559541</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.58706621104153</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.94636104148764</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.1291861651686</v>
       </c>
     </row>
   </sheetData>
@@ -1401,16 +1401,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.00097342946999</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.20047510708257</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.23565994911691</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.67306232450361</v>
+        <v>30.15977432000849</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.58075826656891</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.31309123260088</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.97002129849459</v>
       </c>
     </row>
   </sheetData>
@@ -1459,16 +1459,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.28061459023426</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.77625852956992</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.1484386020593</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.77893481116756</v>
+        <v>21.33203394180041</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.1235341334404</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.56723920071446</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.96313320687516</v>
       </c>
     </row>
   </sheetData>
@@ -1517,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.76796338641605</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.09443066002621</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.25110444427901</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.56045421264457</v>
+        <v>29.1794759299273</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.93146592753233</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.20091830574533</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.64553470318632</v>
       </c>
     </row>
   </sheetData>
@@ -1575,16 +1575,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.40067537241903</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.84860342714547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.53226404332274</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.80028329721894</v>
+        <v>21.11295862971642</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.70321579782459</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.52669981015125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.29752179201447</v>
       </c>
     </row>
   </sheetData>
@@ -1633,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.62283261928525</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.78319676965926</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.61249140886198</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.56241607469411</v>
+        <v>36.62912491012003</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.70698509002735</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.47481437822324</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.74171459886345</v>
       </c>
     </row>
   </sheetData>
@@ -1691,16 +1691,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.82198769430896</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.08823948157289</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.7123615395504</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.48093231700195</v>
+        <v>29.9727542728101</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.08449979417166</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.38241207999003</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.99477612120308</v>
       </c>
     </row>
   </sheetData>
@@ -1749,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.16814870779307</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.66714563908518</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.47626257367669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.76733662777923</v>
+        <v>28.98605870977652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.76444127852132</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.80440817135047</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.25183801387384</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.59464658746195</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.28811067523349</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.97013102388913</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.77847320265413</v>
+        <v>22.14838848907337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.02186657408773</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.93857899269344</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.4564248873326</v>
       </c>
     </row>
   </sheetData>
@@ -1865,16 +1865,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.73680470494457</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.32466780795546</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.05619651212999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>39.91763292367154</v>
+        <v>28.1949362665063</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.22210282527236</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.86738905763659</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.41097260802012</v>
       </c>
     </row>
   </sheetData>
@@ -1923,16 +1923,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.50190642418997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.65189529389913</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.93338557160538</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.12104092507449</v>
+        <v>30.46163722793327</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.32979170824693</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.21040420627238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.86712985335657</v>
       </c>
     </row>
   </sheetData>
@@ -1981,16 +1981,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38452136665508</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.16756338084283</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.64371138864887</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.81646382832096</v>
+        <v>28.20402849279938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.14562576523226</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.85461966442191</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.13846154671648</v>
       </c>
     </row>
   </sheetData>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.87369879911777</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.72971078888531</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.88950462033147</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.23140255781377</v>
+        <v>23.23124814542856</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.89722086071729</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.65089247907359</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.86453399488918</v>
       </c>
     </row>
   </sheetData>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.82626331019467</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.60824326507032</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.15921918831362</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.18601304878916</v>
+        <v>27.7894313476596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.01208790500663</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.8094164593198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.18481755030133</v>
       </c>
     </row>
   </sheetData>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.35604321188033</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.8011641922158</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38.09417770655747</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.72965767738675</v>
+        <v>33.48745715379189</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.57671156154092</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.13163818031938</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.01513705972053</v>
       </c>
     </row>
   </sheetData>
@@ -2213,16 +2213,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.92032374372705</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.76763539031933</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.78030496029801</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.67066487329661</v>
+        <v>25.95065794719087</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.69103750762764</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.83617288739943</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.00551640824738</v>
       </c>
     </row>
   </sheetData>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.30074056951929</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.1708509774321</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.69100113441475</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.12259299298618</v>
+        <v>31.36445310670089</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.11175853606047</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.21442861856085</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.38456804197155</v>
       </c>
     </row>
   </sheetData>
@@ -2329,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.59531335794618</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.33215493480383</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.87550218695587</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.35437901736131</v>
+        <v>24.44991802044692</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.16718947218713</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.83298945651061</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.21199073564606</v>
       </c>
     </row>
   </sheetData>
@@ -2387,16 +2387,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.15829336751105</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.06629784861184</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.8079323199788</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.98108808899511</v>
+        <v>26.03985996492962</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.20158660707555</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.99401388529336</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.40148780461582</v>
       </c>
     </row>
   </sheetData>
@@ -2445,16 +2445,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.33978254906538</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.20869424456587</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.18416344095621</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.91001821790474</v>
+        <v>30.24289569010599</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.9363512352627</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.40364629984023</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.36881801070653</v>
       </c>
     </row>
   </sheetData>
@@ -2503,16 +2503,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.90825126462058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.78012380814464</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.80669123164342</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.09607688905129</v>
+        <v>27.38654808760553</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.15503449166654</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.62539862252026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.70885991390318</v>
       </c>
     </row>
   </sheetData>
@@ -2561,16 +2561,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.49407159999591</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.93246322157316</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.02399992410426</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.9255800981863</v>
+        <v>24.90103436154342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.9821152468776</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.78435468780691</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.64882753652496</v>
       </c>
     </row>
   </sheetData>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.53555012864088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.79144787657434</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.28920584201717</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.03027306333528</v>
+        <v>27.04093679700236</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.34154455150464</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.57813054784367</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.6357319857808</v>
       </c>
     </row>
   </sheetData>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.84741238621578</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.18636365742057</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.64148598671562</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.04334705300398</v>
+        <v>26.30589617175614</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.06489614554844</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.87692169895788</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.55869664582619</v>
       </c>
     </row>
   </sheetData>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.84256226422023</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.72776386810344</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.3056040076119</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.2001058791747</v>
+        <v>28.20362487248477</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.25601028057187</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.7571396958337</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.75643289963034</v>
       </c>
     </row>
   </sheetData>
@@ -2793,16 +2793,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2863212054018</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.82847289096794</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.61821137230564</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.32181254853217</v>
+        <v>22.57347627378207</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.52321110071292</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.02351195463566</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.34954530140294</v>
       </c>
     </row>
   </sheetData>
@@ -2851,16 +2851,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.36458546890037</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.76588579750448</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.8197442112637</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.14629660323681</v>
+        <v>22.11226006803328</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.46327076005125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.99136935798125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.00222984267639</v>
       </c>
     </row>
   </sheetData>
@@ -2909,16 +2909,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.5703916159895</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.95169606640699</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.18322083790626</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.23845370249582</v>
+        <v>21.92317486881756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.04520158319009</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.97284739499886</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.84652872158585</v>
       </c>
     </row>
   </sheetData>
@@ -2967,16 +2967,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.24747909895904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36.39603320184073</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.37426137897289</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.91694301904239</v>
+        <v>28.02699054936334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.22431371067661</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.59817542801737</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.31645769297282</v>
       </c>
     </row>
   </sheetData>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.69556094596653</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.34240530438819</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.02596810994823</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.93755575162304</v>
+        <v>31.32112428646055</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.99475791147189</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.90124715154006</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.39004555911009</v>
       </c>
     </row>
   </sheetData>
@@ -3083,16 +3083,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.99992596407997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.10420766211342</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.38363764763452</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.52515862970431</v>
+        <v>29.18681218874277</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.16244660856157</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.18216431227114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.08531530835705</v>
       </c>
     </row>
   </sheetData>
@@ -3141,16 +3141,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.26151411426735</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.51662858901163</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.40940531054954</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35.38360594294795</v>
+        <v>29.20063587175905</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.61271675275983</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.93317382409452</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.86854711921463</v>
       </c>
     </row>
   </sheetData>
@@ -3199,16 +3199,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.09591843234363</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.55760726516568</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.51899701893329</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.64511302493514</v>
+        <v>28.22285691301572</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.6661590378529</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.04427086085884</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.62569500308848</v>
       </c>
     </row>
   </sheetData>
@@ -3257,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.06810632968464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.2717844308816</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.2035626270047</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.87085213035607</v>
+        <v>27.24660052105874</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.65590023867249</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.32282767061399</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.60080496565642</v>
       </c>
     </row>
   </sheetData>
@@ -3315,16 +3315,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.60946862646578</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.10967362945566</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.95782191460679</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.82876634690049</v>
+        <v>32.54715080057898</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.32290901534565</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.50698435411573</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.24259206335102</v>
       </c>
     </row>
   </sheetData>
@@ -3373,16 +3373,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.46160586868655</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.49680780299888</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.01041592725436</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.8502714367363</v>
+        <v>35.83289867320659</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.667704666972</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.62171789579925</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.04511403462667</v>
       </c>
     </row>
   </sheetData>
@@ -3431,16 +3431,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61801396576575</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.73345044745491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.82067128928736</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.87509649635625</v>
+        <v>31.44575000646174</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.86847859328472</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.31205449940953</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.65542872397077</v>
       </c>
     </row>
   </sheetData>
@@ -3489,16 +3489,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.44817730758838</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.63653826673728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.92291645628075</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.16905626424137</v>
+        <v>33.40227312330591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.02052276737718</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.05513491864438</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.42044560662591</v>
       </c>
     </row>
   </sheetData>
@@ -3547,16 +3547,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.43086819085649</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.63646878861879</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.5285100407864</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.07114775359893</v>
+        <v>24.11773346854808</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.35791946484742</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.66262928793555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.53464941397253</v>
       </c>
     </row>
   </sheetData>
@@ -3605,16 +3605,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.52122868526428</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.95104589402883</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.37476129288775</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.07587127103297</v>
+        <v>24.10848944700979</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.42835008174309</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.11330593253355</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.18454059475962</v>
       </c>
     </row>
   </sheetData>
@@ -3663,16 +3663,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.68975827939162</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.11085058239102</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.13967934045112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.00922723848788</v>
+        <v>31.43354691634952</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.12486443706216</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.94607819209913</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.53929337856205</v>
       </c>
     </row>
   </sheetData>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.14692006726149</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.4899662447266</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.07618259523705</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.66051445516158</v>
+        <v>27.85578256743458</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.75131510512137</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.61658464658979</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.53392625892844</v>
       </c>
     </row>
   </sheetData>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.74771909607412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.99075468614865</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.87840959854562</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.98793528379774</v>
+        <v>32.09302790701112</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.25616031426298</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.80681271042334</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.48908521216915</v>
       </c>
     </row>
   </sheetData>
@@ -3837,16 +3837,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.02891623851714</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.03990494108292</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.52278656629334</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.39743246577617</v>
+        <v>32.9502923357921</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35.0959623323289</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.3122646666996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.14872004247146</v>
       </c>
     </row>
   </sheetData>
@@ -3895,16 +3895,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.86991106310228</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.73555544181115</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.36118118155173</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.11409539464713</v>
+        <v>28.20407039825823</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.23732374406837</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.35514060011259</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.09067581036301</v>
       </c>
     </row>
   </sheetData>
@@ -3953,16 +3953,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.04861238592937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.64129750781805</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.44767801765201</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.6981559044611</v>
+        <v>22.03019836087171</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.3457520429481</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.61605819607149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.99221089901826</v>
       </c>
     </row>
   </sheetData>
@@ -4011,16 +4011,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.24486144550085</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.15575750985569</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.28880360851619</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.2848263655853</v>
+        <v>30.47492497871223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.0281460532161</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.77083697869825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.0012847576198</v>
       </c>
     </row>
   </sheetData>
@@ -4069,16 +4069,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.10338560105978</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.52707233423407</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.03475371557596</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.97503945527393</v>
+        <v>30.53527941097754</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.75973304964123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.80082533356189</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.34106007530161</v>
       </c>
     </row>
   </sheetData>
@@ -4127,16 +4127,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.19529615887982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.26207778788606</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.16642942513103</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.91778436464798</v>
+        <v>25.79904944614619</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.84637254262496</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.76263211459067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.69463014290252</v>
       </c>
     </row>
   </sheetData>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.04703733548873</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.72268366592759</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.70144376865317</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.14129293688643</v>
+        <v>25.26667410400833</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.33062620802428</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.36878052098385</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.82332065904109</v>
       </c>
     </row>
   </sheetData>
@@ -4243,16 +4243,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.47309803057132</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.85981147053562</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.42748016381603</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.38160368430512</v>
+        <v>24.66807714422787</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.7215964881846</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.64844472337708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.24589632433885</v>
       </c>
     </row>
   </sheetData>
@@ -4301,16 +4301,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.6324988022118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.25721966791688</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.7498021136649</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.21088015900215</v>
+        <v>24.27139015833737</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.15732848285019</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.83014157305194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.94502481825796</v>
       </c>
     </row>
   </sheetData>
@@ -4359,16 +4359,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.44968502046329</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.44330072272064</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.12773848787083</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.32482537619425</v>
+        <v>26.32781633644196</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.66017101968164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.97006999338417</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.37320043133868</v>
       </c>
     </row>
   </sheetData>
@@ -4417,16 +4417,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.53682866981685</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.86106020485902</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.2413455981578</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.3156678579921</v>
+        <v>28.37815825601309</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.72371380664527</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.87196571086831</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.86657869258024</v>
       </c>
     </row>
   </sheetData>
@@ -4475,16 +4475,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.27246603819618</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.13520256985089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.3433286077958</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.99668597895659</v>
+        <v>25.41566586704117</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.79399794608815</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.47129178531012</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.20930712756524</v>
       </c>
     </row>
   </sheetData>
@@ -4533,16 +4533,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.94036904222231</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.42851902382382</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.91796602223149</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.32316946917042</v>
+        <v>29.98490245627476</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.39388687611839</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.90583676077522</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.32341308821529</v>
       </c>
     </row>
   </sheetData>
@@ -4591,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.59110904468088</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.53602510600434</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.77151539838355</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.06380993089122</v>
+        <v>26.96606829764005</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.35293880121209</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.82436768054253</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18.11062670501718</v>
       </c>
     </row>
   </sheetData>
@@ -4649,16 +4649,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.24139726926921</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.74506035968516</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.68940478214785</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.75545046320417</v>
+        <v>26.50426266726564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.66289176088681</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.16387617976487</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.14300864653913</v>
       </c>
     </row>
   </sheetData>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.08757347158749</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.72237978171734</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.38382164352265</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.99707732372693</v>
+        <v>30.11872251365862</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.21803906615252</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.01435878141076</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.99565222166145</v>
       </c>
     </row>
   </sheetData>
@@ -4765,16 +4765,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.00200051031216</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.99228361152541</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.03789761331648</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.17613749622142</v>
+        <v>23.27446372326486</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.54025666113753</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.54402708820295</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.51311942707227</v>
       </c>
     </row>
   </sheetData>
@@ -4823,16 +4823,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.11430568106416</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.57772162773308</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.96088709315455</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.61861893367444</v>
+        <v>28.61504644929555</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.16390998617479</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.77607142474627</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.52011325962636</v>
       </c>
     </row>
   </sheetData>
@@ -4881,16 +4881,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.6398055402667</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.13411746668267</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.56776752529507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.90039474551276</v>
+        <v>31.22978211677958</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.31754385186045</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.41816108717744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.44555170382097</v>
       </c>
     </row>
   </sheetData>
@@ -4939,16 +4939,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.55392356098784</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.63403059742981</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.81476414112283</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.19192213583818</v>
+        <v>21.06488698713401</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.63495665741415</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.55271957768311</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.18079040840138</v>
       </c>
     </row>
   </sheetData>
@@ -4997,16 +4997,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.03728516361543</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.11196364583758</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.24230519485842</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.68005114552422</v>
+        <v>34.42764842402869</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.34600726525852</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.23434919593887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.72946769331041</v>
       </c>
     </row>
   </sheetData>
@@ -5055,16 +5055,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.21832613973464</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.40661440437141</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.66351286203176</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.09769818248882</v>
+        <v>24.10620496571949</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.0590815190098</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.95300240322565</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.9088649562134</v>
       </c>
     </row>
   </sheetData>
@@ -5113,16 +5113,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.55107730482803</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22.94888601868024</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.73651284233445</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.19147030498477</v>
+        <v>23.9414242137036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.54438592961279</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.01034662611066</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.7574228012412</v>
       </c>
     </row>
   </sheetData>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.99151783847232</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.59024752914296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.60830788884639</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.17716243408959</v>
+        <v>24.83587376979605</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.94428624842833</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.54297356799971</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.71778044256623</v>
       </c>
     </row>
   </sheetData>
@@ -5229,16 +5229,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.52615687500729</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.76154791950644</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.22155979818498</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.66596716192451</v>
+        <v>27.74918363786531</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.45568952722313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.02411663726036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.43664947520029</v>
       </c>
     </row>
   </sheetData>
@@ -5287,16 +5287,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.56887590607214</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.59772902066193</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.28465906340661</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.53464168773822</v>
+        <v>27.36586900648132</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.04572923240334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.16369826591274</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.45570535705642</v>
       </c>
     </row>
   </sheetData>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.83013072877401</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.44407735486547</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.29991940103669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.83575412950947</v>
+        <v>27.64274084027316</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.55660719448932</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.23036733278715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.20532698051898</v>
       </c>
     </row>
   </sheetData>
@@ -5403,16 +5403,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.79479384028899</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.64308476560269</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.34109493243299</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.38427038467779</v>
+        <v>33.01894787282036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.79430990826796</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.47473048486016</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.00703844033317</v>
       </c>
     </row>
   </sheetData>
@@ -5461,16 +5461,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.25710027230192</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.46147394424103</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.47449092365964</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.13504955019271</v>
+        <v>22.74052601268757</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19.37159178473324</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.9830499768094</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.18820608100302</v>
       </c>
     </row>
   </sheetData>
@@ -5519,16 +5519,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.07277152832475</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.20246624568138</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.66036646340146</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.17600717043953</v>
+        <v>26.38934201426927</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.10266061869221</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.69181291742903</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.36053557677047</v>
       </c>
     </row>
   </sheetData>
@@ -5577,16 +5577,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.23593735227402</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.59667095287234</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.36083895436368</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.89542681509042</v>
+        <v>22.1863210999406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.16046009710387</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.15299694551375</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.09038584176401</v>
       </c>
     </row>
   </sheetData>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.1001399586163</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.18021712315737</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.36403036635842</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.800004828866</v>
+        <v>34.78712183217355</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.99741058876806</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.08906285216627</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.26007492851199</v>
       </c>
     </row>
   </sheetData>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.00948286867809</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.72433980967077</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.2323543811999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.05898852818435</v>
+        <v>24.91844937905982</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.42280574381384</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.40240726840132</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.5236013197222</v>
       </c>
     </row>
   </sheetData>
@@ -5751,16 +5751,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.51015403247593</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.9528792915785</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.4302526512726</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.69449805722328</v>
+        <v>27.42388839312392</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.21084539163734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.49373802323326</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.85886579957321</v>
       </c>
     </row>
   </sheetData>
@@ -5809,16 +5809,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.21839988710272</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.24326290412223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.57880293393754</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.22792026194234</v>
+        <v>29.00770174582203</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.92466383320315</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.52806813210874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.55227103763787</v>
       </c>
     </row>
   </sheetData>
@@ -5867,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.45619892491549</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.89169420091021</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.72537621301495</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.95792304297392</v>
+        <v>26.44662818055015</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.24401640287993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.45103135048782</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.15835397332118</v>
       </c>
     </row>
   </sheetData>
@@ -5925,16 +5925,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.5367883360896</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.06054271195938</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.56556798680212</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.77632738822557</v>
+        <v>30.26693435441183</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.75516976857664</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.09937644125309</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.6433489767918</v>
       </c>
     </row>
   </sheetData>
@@ -5983,16 +5983,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.87431183330341</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.94692400661581</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.07241105103279</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.48714902996197</v>
+        <v>31.80880664821468</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.58674143986898</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.66096435036352</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.14252355766992</v>
       </c>
     </row>
   </sheetData>
@@ -6041,16 +6041,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.28804437206716</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.5161781952843</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.02944847089632</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.04972377352954</v>
+        <v>26.79820526886021</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.44366536384704</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.09161854426905</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.58251105960896</v>
       </c>
     </row>
   </sheetData>
@@ -6099,16 +6099,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.09208201090574</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.56641858468279</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.87100624876769</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.11744000254573</v>
+        <v>25.14921722801358</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.41126013225195</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.44349325319462</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.37330438322333</v>
       </c>
     </row>
   </sheetData>
@@ -6157,16 +6157,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.6042367180534</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.55941168815474</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.5606384172928</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.22087899990748</v>
+        <v>30.18028094044847</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.14470610003886</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.87717377296665</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.31553663702205</v>
       </c>
     </row>
   </sheetData>
@@ -6215,16 +6215,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.70037050731483</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.4527311125187</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.26824886989669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.36955785955943</v>
+        <v>30.44417730468718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.82319957024341</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.85461637683699</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.85216242404582</v>
       </c>
     </row>
   </sheetData>
@@ -6273,16 +6273,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.56230000286084</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.80608404919499</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.7645897051958</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.82275239365206</v>
+        <v>22.71441460293233</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.00054234330656</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.61777512942399</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.55580108063508</v>
       </c>
     </row>
   </sheetData>
@@ -6331,16 +6331,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.53572057726154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.02992965608254</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.82032148612855</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.91612757665646</v>
+        <v>25.8385547244549</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.45824090839372</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.59962185523487</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.79536989591096</v>
       </c>
     </row>
   </sheetData>
@@ -6389,16 +6389,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.16653939722251</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.32428933720114</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.95302234625871</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.93047292694977</v>
+        <v>24.42897552912831</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.32771099897143</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.20733873205398</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.54265040696408</v>
       </c>
     </row>
   </sheetData>
@@ -6447,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61723920407733</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.17616179467485</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.15649184010281</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.48749443299902</v>
+        <v>27.65542305872229</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.1462551668076</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.9045856241093</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.9407132323918</v>
       </c>
     </row>
   </sheetData>
@@ -6505,16 +6505,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.27507638833644</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.73635719241777</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.4811718559404</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.08534992206389</v>
+        <v>24.67922119226516</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.83390914932597</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.79451072378921</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.09434257921267</v>
       </c>
     </row>
   </sheetData>
@@ -6563,16 +6563,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.31170178645302</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.00284011107468</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.67058796237478</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.14703198350104</v>
+        <v>28.67877275909501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.91556958078093</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.38191192016169</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.74860456753898</v>
       </c>
     </row>
   </sheetData>
@@ -6621,16 +6621,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.73112912581223</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.76643767425199</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.65943432086317</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.25857513308554</v>
+        <v>22.0731170504105</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.16004965737533</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.44158418617459</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.36150740658137</v>
       </c>
     </row>
   </sheetData>
@@ -6679,16 +6679,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.64104765316482</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.12923507185468</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.83012380532293</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.02836763702145</v>
+        <v>32.00077656538721</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.70711523673564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.4435044797678</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.24955910189116</v>
       </c>
     </row>
   </sheetData>
@@ -6737,16 +6737,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.61226795181475</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.60288199813402</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.85278773938407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.3474994382156</v>
+        <v>25.19567468878275</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.60406713832348</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.28600773722486</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.08242625956613</v>
       </c>
     </row>
   </sheetData>
@@ -6795,16 +6795,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.75881364159382</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.28922135434799</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.33769750180796</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.52400875357747</v>
+        <v>28.50338582561839</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.83168702144572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.23917657617945</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.10880650165323</v>
       </c>
     </row>
   </sheetData>
@@ -6853,16 +6853,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.46067877986412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.52433203396068</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.73966024819799</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.48661597926545</v>
+        <v>21.26055709044939</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.3385401286148</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.50636328617014</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.29310310055715</v>
       </c>
     </row>
   </sheetData>
@@ -6911,16 +6911,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.77559759079321</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.63896980122468</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.49106890355869</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.69521260193334</v>
+        <v>23.55314858895317</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.05251646204882</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.26794245079583</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.98599346950028</v>
       </c>
     </row>
   </sheetData>
@@ -6969,16 +6969,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.08324609740851</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.94066076268728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.24622219754747</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.57343437778933</v>
+        <v>21.89695340200416</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.89618107664966</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.52807293328994</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19.80057551866001</v>
       </c>
     </row>
   </sheetData>
@@ -7027,16 +7027,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.42887836127492</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.67427730880395</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.53759532105384</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.31080827701128</v>
+        <v>20.69380706835617</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.05863084913392</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.73574620660295</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.59156185753174</v>
       </c>
     </row>
   </sheetData>
@@ -7085,16 +7085,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.22453504617758</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.98567760877527</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.24004215276875</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.83443434210572</v>
+        <v>27.58685968328933</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.46401183172408</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.86297903620214</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.75240407575482</v>
       </c>
     </row>
   </sheetData>
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.20131223091251</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.17382195286744</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.55558405117642</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.86377872449048</v>
+        <v>22.65544118125821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.88757707756243</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.24677796983556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.38337943326528</v>
       </c>
     </row>
   </sheetData>
@@ -7201,16 +7201,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.42378324140617</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.36914664976506</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.49703311944107</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.88946328067515</v>
+        <v>38.86614171024127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.91817210283003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.69717009663016</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.95783777645725</v>
       </c>
     </row>
   </sheetData>
@@ -7259,16 +7259,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.62070249617978</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.12747647086523</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.85696009145059</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.98038075040492</v>
+        <v>26.32192150550967</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.43124847062523</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.91369045357024</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.30119678030779</v>
       </c>
     </row>
   </sheetData>
@@ -7317,16 +7317,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.73206314228344</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.28854364255366</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.45204334075875</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.60273857791254</v>
+        <v>18.51985735329006</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.73221625683977</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.80867900633097</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.1799416768994</v>
       </c>
     </row>
   </sheetData>
@@ -7375,16 +7375,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.34092535352846</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.8140607144605</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.26027554712361</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.10457290776556</v>
+        <v>27.6886020090304</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.76351689594262</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.85306785654855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.42364324888935</v>
       </c>
     </row>
   </sheetData>
@@ -7433,16 +7433,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.40526232838031</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.47934309397779</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.38404589750905</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.4150457512902</v>
+        <v>22.10126612256433</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.81115187186941</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.9116145599743</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.93692230077969</v>
       </c>
     </row>
   </sheetData>
@@ -7491,16 +7491,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.58141713756175</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.16783882558407</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.56690082005774</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.74232508714947</v>
+        <v>32.27762314956038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.82903880727734</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.05205633952584</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.34737219355276</v>
       </c>
     </row>
   </sheetData>
@@ -7549,16 +7549,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.73271127721324</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.42821193211716</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.51742940588569</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.5938168558411</v>
+        <v>30.183629645404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.50291069239662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.97046975549145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.08598728059193</v>
       </c>
     </row>
   </sheetData>
@@ -7607,16 +7607,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.65140088994234</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.16858925052891</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.49124860953419</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.32368560325879</v>
+        <v>27.28445111348368</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.33484503270961</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.27791645122181</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.20963878485355</v>
       </c>
     </row>
   </sheetData>
@@ -7665,16 +7665,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.25251389061006</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.77829120775837</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.60290437838869</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.98857814446581</v>
+        <v>23.98920858312287</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.03386115907617</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.04206996574823</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.16584325765144</v>
       </c>
     </row>
   </sheetData>
@@ -7723,16 +7723,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.26308296427621</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.40063364513722</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.03953019780866</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.56082755304413</v>
+        <v>29.64700686538814</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.48564934019656</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.17142716823309</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.38878364298774</v>
       </c>
     </row>
   </sheetData>
@@ -7781,16 +7781,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.08156139356045</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.85489317519463</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.28792771194696</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.42438934488316</v>
+        <v>25.59173997336848</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.638710986114</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.2905587210153</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.3258720041391</v>
       </c>
     </row>
   </sheetData>
@@ -7839,16 +7839,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.78878206894154</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.11753894118117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.06894597525298</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.61636722753994</v>
+        <v>25.56528195901148</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.33403079670989</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.29692794258298</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.27667695692479</v>
       </c>
     </row>
   </sheetData>
@@ -7897,16 +7897,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.29840408409904</v>
-      </c>
-      <c r="C2" t="n">
-        <v>39.25552763274315</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.11857948463658</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.46089863498251</v>
+        <v>26.88879456093317</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.94127594826682</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.89867727851715</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.25302646236927</v>
       </c>
     </row>
   </sheetData>
@@ -7955,16 +7955,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.36753778414554</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.8350090695754</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.48413223926529</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.59100021520323</v>
+        <v>25.77180008481192</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.70363432761039</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.54487220696171</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.4344617669161</v>
       </c>
     </row>
   </sheetData>
@@ -8013,16 +8013,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.36551327292732</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.66754442564242</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.90587993975663</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.71861398335534</v>
+        <v>25.95852305093503</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.6946448985599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.51438098408219</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.86092465029095</v>
       </c>
     </row>
   </sheetData>
@@ -8071,16 +8071,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.72454383217152</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.9205307932515</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.49322021183077</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.3998533595271</v>
+        <v>28.2143315722578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.45134460764371</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.30165369059194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.46586402776567</v>
       </c>
     </row>
   </sheetData>
@@ -8129,16 +8129,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.42918555469345</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.41902797367771</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.31265750896958</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.11550235096016</v>
+        <v>32.8394410598122</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.06834003399323</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.87497466050976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.88624747893393</v>
       </c>
     </row>
   </sheetData>
@@ -8187,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.36653586975332</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.02869113328206</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.62630687405999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.09537173915441</v>
+        <v>25.34084135642052</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.18649252936661</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.16770113768255</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.88788476984583</v>
       </c>
     </row>
   </sheetData>
@@ -8245,16 +8245,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.50510996408562</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.69145008294715</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.93146627979407</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.65171729149739</v>
+        <v>27.04579654702803</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.64540358232537</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.86077955609711</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.97358151540344</v>
       </c>
     </row>
   </sheetData>
@@ -8303,16 +8303,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.79088904857825</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.61222246312339</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.07204736874858</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.86840273509561</v>
+        <v>27.7208129805029</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.05851605251463</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.16140975307292</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.67358341456604</v>
       </c>
     </row>
   </sheetData>
@@ -8361,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.48528764375502</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.91078074265446</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.52118600238613</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.64985507246607</v>
+        <v>30.04874280743971</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.08564080822314</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.54177853984181</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.80210025260325</v>
       </c>
     </row>
   </sheetData>
@@ -8419,16 +8419,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.64674715003235</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37.62434928981678</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.682859048181</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.28504422880145</v>
+        <v>29.4613580539129</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.18657864793492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.33789799035717</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.95609105690044</v>
       </c>
     </row>
   </sheetData>
@@ -8477,16 +8477,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.67045092998618</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.74965202702556</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.27587096199368</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.27930707154471</v>
+        <v>26.46231554728887</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.929290618973</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.22628989324286</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.72413673756473</v>
       </c>
     </row>
   </sheetData>
@@ -8535,16 +8535,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.74443581155417</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18.5995480895363</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.39145963162835</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.61731963616262</v>
+        <v>21.41897570264181</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.56049175388583</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.21802328034517</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.27172051120963</v>
       </c>
     </row>
   </sheetData>
@@ -8593,16 +8593,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.11491356145943</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.70634943053948</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.11724884615669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.446607310166</v>
+        <v>27.67102325505907</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.67892415963676</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.03398627892507</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.3555632075896</v>
       </c>
     </row>
   </sheetData>
@@ -8651,16 +8651,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.08270156572236</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.20071277231349</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.50225799005791</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.18613951060583</v>
+        <v>26.72445726528172</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.28768021196139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.7310539770814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.98485867980455</v>
       </c>
     </row>
   </sheetData>
@@ -8709,16 +8709,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.35547926245935</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.92839456046226</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.80071017087214</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.30775598343965</v>
+        <v>28.3771135378591</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.58186540868775</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.5885325476331</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.06820384770656</v>
       </c>
     </row>
   </sheetData>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.43561014697074</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.75454952659655</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.30520505463432</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.87718845345925</v>
+        <v>24.09349947382827</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.61065126498669</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.15266117122997</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.18486021919026</v>
       </c>
     </row>
   </sheetData>
@@ -8825,16 +8825,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.45753057896062</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.02972508196771</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.45097066773948</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.10317158402287</v>
+        <v>27.28564991007776</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.55775852317628</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.63026306388415</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.51876770120744</v>
       </c>
     </row>
   </sheetData>
@@ -8883,16 +8883,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.4447514784652</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.68606379422872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.09539880197706</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.19402267751637</v>
+        <v>29.78330462021887</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.06827229361633</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.61606191125675</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.40613823636717</v>
       </c>
     </row>
   </sheetData>
@@ -8941,16 +8941,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.23128281323094</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.74027531780411</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.7174807936711</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.83005634366582</v>
+        <v>28.32651349189058</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34.23052832841858</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.07098614392054</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.79116687703999</v>
       </c>
     </row>
   </sheetData>
@@ -8999,16 +8999,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.53711666956806</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.46992495086997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>20.98876453244543</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.11449923411589</v>
+        <v>28.76262382329373</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.37825458659769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.65799136654011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.3221611381101</v>
       </c>
     </row>
   </sheetData>
@@ -9057,16 +9057,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.51378102497732</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.62026480818406</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.22445337456463</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.69080497189766</v>
+        <v>28.50778196215725</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.5120388375385</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.89113249897383</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.25723962113788</v>
       </c>
     </row>
   </sheetData>
@@ -9115,16 +9115,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.55800986545785</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.74018105285802</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.49230841363843</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.84601347002296</v>
+        <v>31.38118537256718</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.21750037783135</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.04774570215092</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.75284393068488</v>
       </c>
     </row>
   </sheetData>
@@ -9173,16 +9173,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.51583495505674</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33.9882646736765</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.53356490209448</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.68226491458693</v>
+        <v>34.66329979975693</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.01212269354804</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.87005346912245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.30489148395782</v>
       </c>
     </row>
   </sheetData>
@@ -9231,16 +9231,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.41778396148619</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.09024930606929</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.58361099633112</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.13978207590538</v>
+        <v>22.75886074835773</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.30461828498004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.41290468062814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.09276237196323</v>
       </c>
     </row>
   </sheetData>
@@ -9289,16 +9289,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.55212959424263</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.51346777298009</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.53907874367088</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.05133888416304</v>
+        <v>27.75931163462732</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.88688053316185</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.39419409250813</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.11879190786576</v>
       </c>
     </row>
   </sheetData>
@@ -9347,16 +9347,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.29024998148098</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.34880044905264</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.22054528136674</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.92886193022277</v>
+        <v>24.08711903106542</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.65959259603601</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.39404939167582</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.35390887675413</v>
       </c>
     </row>
   </sheetData>
@@ -9405,16 +9405,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.64771510964102</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.60028426928867</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.61056259250315</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.87767581554468</v>
+        <v>28.43671070322688</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.12375474615972</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.66659994626829</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.41300682169429</v>
       </c>
     </row>
   </sheetData>
@@ -9463,16 +9463,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.48338857994118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.66775866276802</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.34572695575272</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.38903759038313</v>
+        <v>24.66520963549756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.44167402293575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.10894201069718</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.70258635822455</v>
       </c>
     </row>
   </sheetData>
@@ -9521,16 +9521,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.43049903436569</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.92877364139211</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.68693152720535</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.7068525724662</v>
+        <v>26.12411694303068</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.0302569294917</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.01721676778679</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.12009938449569</v>
       </c>
     </row>
   </sheetData>
@@ -9579,16 +9579,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.71963387398924</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.54428123013414</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.01799397578532</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.9760716806741</v>
+        <v>34.87312875018191</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.45672715206474</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.80981240180102</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.6271555211164</v>
       </c>
     </row>
   </sheetData>
@@ -9637,16 +9637,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.53054425762647</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.9872467251596</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.45272401271436</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.49048935645866</v>
+        <v>24.08973829612938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.24431489806376</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.38803932333918</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.39372912704992</v>
       </c>
     </row>
   </sheetData>
@@ -9695,16 +9695,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.95112128518456</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.22540212545389</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.30322708572568</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.72153363855868</v>
+        <v>25.31181465130197</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.58770901674938</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.1256592153217</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.21939266646418</v>
       </c>
     </row>
   </sheetData>
@@ -9753,16 +9753,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.55346017071397</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.70411047517615</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.80232106615885</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.07132109790517</v>
+        <v>27.21249628578706</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.58521127774445</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.91000227581996</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.70573436810009</v>
       </c>
     </row>
   </sheetData>
@@ -9811,16 +9811,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.12325312682031</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.99729121739196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.49432638856047</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.92926511806226</v>
+        <v>29.55814831348868</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.19274626285588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.84116379791065</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.72614298790558</v>
       </c>
     </row>
   </sheetData>
@@ -9869,16 +9869,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.22684681614589</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.92745040385268</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.64999026136199</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.96852457431837</v>
+        <v>24.8868393082131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.48398372690385</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.70811040180071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.77351508779259</v>
       </c>
     </row>
   </sheetData>
@@ -9927,16 +9927,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.43939459972689</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.68614929347193</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.0121666181811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.15152318450034</v>
+        <v>31.01967097125713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.79997433041694</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.68435429652893</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.99038885358258</v>
       </c>
     </row>
   </sheetData>
@@ -9985,16 +9985,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.78496285812741</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.6065936120151</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.34874848208294</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.12483075186657</v>
+        <v>30.93202741230708</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.47882456243691</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.30308137381665</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33.15710857592367</v>
       </c>
     </row>
   </sheetData>
@@ -10043,16 +10043,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.6847076140374</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.25122411921726</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.5725425380659</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.7488252569001</v>
+        <v>29.01946939221301</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.4157692569574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.13925301945714</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.92572198799279</v>
       </c>
     </row>
   </sheetData>
@@ -10101,16 +10101,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.69894190581788</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.52934553257462</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.49063330829811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.40889348583611</v>
+        <v>31.10863488017363</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.66490169048856</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.42836773214349</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.96968000614776</v>
       </c>
     </row>
   </sheetData>
@@ -10159,16 +10159,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.81437465063341</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.97610704201825</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.97324429385035</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.15073695082612</v>
+        <v>24.56037417309588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.77527355337973</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.53338434069589</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.10792596892806</v>
       </c>
     </row>
   </sheetData>
@@ -10217,16 +10217,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.75961116829694</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.57903868476672</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.86325509154755</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.17816144104314</v>
+        <v>32.87853443362075</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.71991675561884</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.70340516373883</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.44196160807522</v>
       </c>
     </row>
   </sheetData>
@@ -10275,16 +10275,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.58887609518634</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.11017707524821</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.52562283262777</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34.03397735872694</v>
+        <v>30.18558727060439</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.96623263206363</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.86809624055049</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.22819464655248</v>
       </c>
     </row>
   </sheetData>
@@ -10333,16 +10333,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.70499804235228</v>
-      </c>
-      <c r="C2" t="n">
-        <v>23.73150265532229</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.32370036527516</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.7028055738104</v>
+        <v>29.21321158133292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.04697422785859</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.68083111936361</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.73756518865655</v>
       </c>
     </row>
   </sheetData>
@@ -10391,16 +10391,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.48984836589432</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.71453601370998</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.85395150139458</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.00227415840569</v>
+        <v>25.60795157030872</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.04320946417451</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.95558339489225</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.17275852343621</v>
       </c>
     </row>
   </sheetData>
@@ -10449,16 +10449,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.14616436685747</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.33976553239929</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.33420695741589</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.74311700122147</v>
+        <v>27.39158169706514</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.50251519731247</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.4231178663336</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.64281911316975</v>
       </c>
     </row>
   </sheetData>
@@ -10507,16 +10507,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.2067437635604</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.54243023537781</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.87145809384086</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.43886159324275</v>
+        <v>23.97366073873922</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.06214416670048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.43621794413496</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.00677958662218</v>
       </c>
     </row>
   </sheetData>
@@ -10565,16 +10565,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.16115206303732</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.75517563237857</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21.36696593741391</v>
-      </c>
-      <c r="E2" t="n">
-        <v>28.69799433609796</v>
+        <v>27.32858860839882</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.13441594440024</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30.18290130286159</v>
+      </c>
+      <c r="E2" t="n">
+        <v>18.13535868418249</v>
       </c>
     </row>
   </sheetData>
@@ -10623,16 +10623,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.43757962940773</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21.06967003116378</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.78543731519757</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.86695963685291</v>
+        <v>24.1609030485535</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.14011140774072</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.18962671192734</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.19078677222784</v>
       </c>
     </row>
   </sheetData>
@@ -10681,16 +10681,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.53529413302474</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.80598171790349</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.87957663378016</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.710944182083</v>
+        <v>19.65478302748697</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.62241161358844</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.13720433601238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30.47099538339859</v>
       </c>
     </row>
   </sheetData>
@@ -10739,16 +10739,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.22588039174817</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.14740676670073</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.60465628483396</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.2970683062965</v>
+        <v>29.11511889931615</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.29954874616203</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.56324399285857</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.62734884717972</v>
       </c>
     </row>
   </sheetData>
@@ -10797,16 +10797,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.02334737463848</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.73444184881296</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.56548275546553</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.3349158861665</v>
+        <v>27.9609128954013</v>
+      </c>
+      <c r="C2" t="n">
+        <v>29.82346600331555</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.80081817917878</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.713141966218</v>
       </c>
     </row>
   </sheetData>
@@ -10855,16 +10855,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.01474155646964</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.67612464245869</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.0594445726864</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.27284787973424</v>
+        <v>33.85170997367381</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.96833948551048</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.05650274359567</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.94498810523322</v>
       </c>
     </row>
   </sheetData>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.40234149026404</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.53761799117198</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.82221978047283</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.92208041890649</v>
+        <v>25.42376988373145</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30.03022524089154</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.14792235619611</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.66508368628625</v>
       </c>
     </row>
   </sheetData>
@@ -10971,16 +10971,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.24065048473133</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.76445708617059</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27.20274445641254</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.48176169194657</v>
+        <v>32.63273484665579</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.88089883665071</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.77702467071747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.05537806501688</v>
       </c>
     </row>
   </sheetData>
@@ -11029,16 +11029,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.45455621453894</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.45358190932311</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.1099764570839</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.69622722862463</v>
+        <v>23.09684320520529</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.54411017950945</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.73108725945863</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.78479986771471</v>
       </c>
     </row>
   </sheetData>
@@ -11087,16 +11087,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.1669417680338</v>
-      </c>
-      <c r="C2" t="n">
-        <v>27.77976678480196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.03289216544004</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.54158758621421</v>
+        <v>26.17861793485377</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28.68278212438683</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.14211924101919</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.89758677886316</v>
       </c>
     </row>
   </sheetData>
@@ -11145,16 +11145,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.56568924672953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.39260014085091</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.72521440985132</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.16364801115536</v>
+        <v>25.31384294602669</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.65334628896885</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.15198583919373</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.99393387441218</v>
       </c>
     </row>
   </sheetData>
@@ -11203,16 +11203,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.818029309787</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.23195081976495</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30.95954651812355</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.1104656477183</v>
+        <v>32.14735267987018</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.01628136439751</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.21798588574056</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.63147950322249</v>
       </c>
     </row>
   </sheetData>
@@ -11261,16 +11261,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.92326940201664</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.1390104457284</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.3631366968842</v>
-      </c>
-      <c r="E2" t="n">
-        <v>36.72069999962174</v>
+        <v>25.92797701702281</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.67817121827519</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.11498396620335</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.69944084774776</v>
       </c>
     </row>
   </sheetData>
@@ -11319,16 +11319,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.31554321148539</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32.12415862317662</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.38248396365938</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33.41980394414498</v>
+        <v>32.62735139059223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.4358624656574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.35531852590518</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.62643965285776</v>
       </c>
     </row>
   </sheetData>
@@ -11377,16 +11377,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.73362505016982</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.50922723300449</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.354124341315</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.25525682914443</v>
+        <v>32.13727666331427</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.04780463819739</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.3655544986001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.13899334566978</v>
       </c>
     </row>
   </sheetData>
@@ -11435,16 +11435,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.23739880111637</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.20577676435479</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.89268519330775</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.8452274502844</v>
+        <v>27.15076250108063</v>
+      </c>
+      <c r="C2" t="n">
+        <v>23.99162741665273</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.95488265987055</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.06000578630164</v>
       </c>
     </row>
   </sheetData>
@@ -11493,16 +11493,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.62996845929269</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.15254128701596</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.85669859523163</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.22672842065663</v>
+        <v>28.35585647475261</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.12909208305106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.58221934749419</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.46273815101159</v>
       </c>
     </row>
   </sheetData>
@@ -11551,16 +11551,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.10362327552092</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.00657571956171</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.18036297115513</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.4522946319598</v>
+        <v>21.54989679169798</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.60976741886375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.69812837698187</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.32917113019997</v>
       </c>
     </row>
   </sheetData>
@@ -11609,16 +11609,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2148783048662</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.98551227481525</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.22916809670898</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.27235367059615</v>
+        <v>28.32213184704242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27.36808084779412</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.29304343299396</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.55665904573915</v>
       </c>
     </row>
   </sheetData>
@@ -11667,16 +11667,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.19193622918903</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34.99631031334548</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25.70752563357608</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.89368272600924</v>
+        <v>27.11180457357712</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.9271345328478</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.36338723398087</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.63121686239181</v>
       </c>
     </row>
   </sheetData>
@@ -11725,16 +11725,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.00260785590583</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.20588847955089</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.2723775260034</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21.33409598687366</v>
+        <v>19.82755024973968</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24.59431817208739</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.02909919806351</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23.83269339491443</v>
       </c>
     </row>
   </sheetData>
@@ -11783,16 +11783,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.22727156247125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31.34686761731635</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26.79435473655084</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.81207774791658</v>
+        <v>29.51932102354537</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.07248908128884</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.46195638304598</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.88274848349861</v>
       </c>
     </row>
   </sheetData>
@@ -11841,16 +11841,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.07907587331125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.93984354996116</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29.46876466585767</v>
-      </c>
-      <c r="E2" t="n">
-        <v>25.82726799265308</v>
+        <v>25.8043515400351</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.90141081282085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.38395194406707</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.27956280305696</v>
       </c>
     </row>
   </sheetData>
@@ -11899,16 +11899,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.90858572233839</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.63774903596466</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.37215242758549</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.81350800657257</v>
+        <v>31.87790693951342</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.36378843149965</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.95966434742031</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.84520497720881</v>
       </c>
     </row>
   </sheetData>
@@ -11957,16 +11957,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.23652437535225</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.59693180192017</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31.80212477109368</v>
-      </c>
-      <c r="E2" t="n">
-        <v>30.52459273051716</v>
+        <v>27.22830978476836</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.09731717931951</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.33339675135283</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.188648450909</v>
       </c>
     </row>
   </sheetData>
@@ -12015,16 +12015,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.19795015408201</v>
-      </c>
-      <c r="C2" t="n">
-        <v>24.63356575373142</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.37452734192947</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24.47653877710542</v>
+        <v>26.07635786305727</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25.22336259176463</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.05750081598769</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.17881313721213</v>
       </c>
     </row>
   </sheetData>
@@ -12073,16 +12073,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.73767836115437</v>
-      </c>
-      <c r="C2" t="n">
-        <v>29.14170570809938</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.8793010769412</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.41181087193388</v>
+        <v>27.22329452691969</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33.77899457807567</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.53873049500115</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.47752499832614</v>
       </c>
     </row>
   </sheetData>
@@ -12131,16 +12131,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.47996364111591</v>
-      </c>
-      <c r="C2" t="n">
-        <v>26.79815424796553</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.75844043298636</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27.45634338999608</v>
+        <v>27.44279084788225</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26.98902782128183</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.86788307369867</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.38710294123968</v>
       </c>
     </row>
   </sheetData>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.14544430646333</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28.42748587895924</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.32745623209004</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31.57016577346349</v>
+        <v>27.48871182893316</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.88412194904665</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.41212358523708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.46736904507151</v>
       </c>
     </row>
   </sheetData>
